--- a/public/templates/forms/A-126-EncryptionImplementationVerificationRecords-FORM.xlsx
+++ b/public/templates/forms/A-126-EncryptionImplementationVerificationRecords-FORM.xlsx
@@ -3,12 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="23380" windowHeight="21660" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="23380" windowHeight="21660" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Log" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Log!$11:$11</definedName>
+  </definedNames>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -16,7 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="11">
     <font>
       <name val="Aptos"/>
@@ -187,7 +192,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -244,6 +249,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -614,14 +622,14 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
+    <row r="10" ht="34.7" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>« Add one row per system or data category in scope. Record the mechanism actually in use and the validation performed; key the bar to the Encryption Standards Document. »</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="27.75" customHeight="1">
+    <row r="11" ht="34.7" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Ref #</t>
@@ -770,7 +778,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="29.75" customHeight="1">
+    <row r="24" ht="34.7" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
           <t>« Summarize exceptions from the entries above. Mirror each exception into the Risk / Finding Register (POA&amp;M) with an owner and remediation date. »</t>
@@ -957,7 +965,7 @@
       <c r="E46" s="11" t="n"/>
       <c r="F46" s="11" t="n"/>
     </row>
-    <row r="48" ht="30" customHeight="1">
+    <row r="48" ht="50.5" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Drafter’s note (internal, delete before publishing): the Agency fills [Agency Name], version, dates, and roles, and records one row per system or data category that requires encryption. The bar being verified is the Encryption Standards Document; do not restate algorithms here. Keep the / CJIS marker only if the Agency stores or transmits CJIS-regulated data on systems it controls.</t>
@@ -996,8 +1004,18 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="C12:C21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Encryption Requirement (at rest " prompt="Select a value" type="list">
+      <formula1>"At rest,In transit,Voice"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation sqref="G12:G21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Result (Compliant / Exception)" prompt="Select a value" type="list">
+      <formula1>"Compliant,Exception"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -1023,14 +1041,14 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="43.5" customHeight="1">
+    <row r="2" ht="161.4" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>How to use this template: fill the header block on the Log tab, replace every [BRACKETED] field, record one row per system or data category in scope, then delete every « » note before publishing.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="29.75" customHeight="1">
+    <row r="3" ht="113.9" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Placeholder key:  [BRACKETED] = fill in   ·   « » = guidance to delete.  Classification, findings, sign-off, retention and revision history live on the Log tab.</t>
@@ -1110,7 +1128,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
+    <row r="9" ht="50.5" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Encryption Requirement (at rest / in transit / voice)</t>
@@ -1132,7 +1150,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
+    <row r="10" ht="50.5" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
         <is>
           <t>Mechanism in Use (algorithm, protocol, key length)</t>
@@ -1154,7 +1172,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
+    <row r="11" ht="34.7" customHeight="1">
       <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Validation / Test Performed</t>
@@ -1192,13 +1210,11 @@
           <t>Required</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
+      <c r="D12" s="23">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="13" ht="34.7" customHeight="1">
       <c r="A13" s="15" t="inlineStr">
         <is>
           <t>Result (Compliant / Exception)</t>
@@ -1220,7 +1236,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="20" customHeight="1">
+    <row r="14" ht="34.7" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
           <t>Exception &amp; Remediation Date</t>
@@ -1253,7 +1269,7 @@
       </c>
       <c r="B16" s="16" t="n"/>
     </row>
-    <row r="17" ht="42" customHeight="1">
+    <row r="17" ht="90.1" customHeight="1">
       <c r="A17" s="17" t="inlineStr">
         <is>
           <t>What minimum-viable upkeep looks like at each PSAP size. Keep all three rows while this ships as a template; once adopted, keep the one that fits.</t>
@@ -1273,7 +1289,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="42" customHeight="1">
+    <row r="19" ht="50.5" customHeight="1">
       <c r="A19" s="18" t="inlineStr">
         <is>
           <t>Small (1–5, no in-house IT)</t>
@@ -1285,7 +1301,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="50.5" customHeight="1">
       <c r="A20" s="18" t="inlineStr">
         <is>
           <t>Medium (6–25, shared county IT)</t>
@@ -1297,7 +1313,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="50.5" customHeight="1">
       <c r="A21" s="18" t="inlineStr">
         <is>
           <t>Large (25+, dedicated IT/security)</t>
@@ -1311,6 +1327,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>